--- a/output/pdf_financials_xlsx/SGR.UN.xlsx
+++ b/output/pdf_financials_xlsx/SGR.UN.xlsx
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>10.962</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>13.174</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>11.855</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>13.431</v>
@@ -2160,25 +2160,25 @@
         <v>1.11</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.412</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.362</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>14.038</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>20.392</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>23.587</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>22.668</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>21.819</v>
       </c>
     </row>
     <row r="35">
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>10.962</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>13.174</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>11.855</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>13.431</v>
@@ -2252,25 +2252,25 @@
         <v>1.11</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.412</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.362</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>14.038</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>20.392</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>23.587</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>22.668</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>21.819</v>
       </c>
     </row>
     <row r="37">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>12.197</v>
+        <v>1.235</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.661</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.724</v>
+        <v>1.869</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.858</v>
@@ -2804,25 +2804,25 @@
         <v>14.955</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.716</v>
+        <v>3.304</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>23.783</v>
+        <v>21.421</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.184</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>32.258</v>
+        <v>11.866</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>35.556</v>
+        <v>11.969</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>35.028</v>
+        <v>12.36</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>34.605</v>
+        <v>12.786</v>
       </c>
     </row>
     <row r="49">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGR.UN.xlsx
+++ b/output/pdf_financials_xlsx/SGR.UN.xlsx
@@ -1180,10 +1180,10 @@
         <v>-17.464</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-29.071</v>
+        <v>-40.625</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>47.306</v>
+        <v>63.116</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>6.482</v>
@@ -1198,7 +1198,7 @@
         <v>53.941</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>138.514</v>
+        <v>105.194</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>22.996</v>
@@ -1226,10 +1226,10 @@
         <v>17.929</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>11.554</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-15.81</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-4.021</v>
@@ -1244,7 +1244,7 @@
         <v>33.487</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.359</v>
+        <v>33.679</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-1.332</v>
@@ -1816,10 +1816,10 @@
         <v>-17.464</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-29.071</v>
+        <v>-40.625</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>47.306</v>
+        <v>63.116</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>6.482</v>
@@ -1834,7 +1834,7 @@
         <v>53.941</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>138.514</v>
+        <v>105.194</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>22.996</v>
@@ -1908,10 +1908,10 @@
         <v>-17.464</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-29.071</v>
+        <v>-40.625</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>47.306</v>
+        <v>63.116</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>6.482</v>
@@ -1926,7 +1926,7 @@
         <v>53.941</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>138.514</v>
+        <v>105.194</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>22.996</v>
@@ -2026,10 +2026,10 @@
         <v>-102.662620247366</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-28.44061538461539</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>25.04911591355599</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>62.03332304844184</v>
@@ -2044,7 +2044,7 @@
         <v>62.08079197641868</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.2591795775156302</v>
+        <v>32.01608456756089</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>5.792311706383719</v>
@@ -2421,40 +2421,40 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.168</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>2.877</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>3.172</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>3.453</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>8.273</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>6.893</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>5.964</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>6.739</v>
       </c>
     </row>
     <row r="41">
@@ -2467,40 +2467,40 @@
         <v>1.23</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8.617000000000001</v>
+        <v>9.116</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>7.344</v>
+        <v>8.116</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>6.877</v>
+        <v>8.045</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>9.875999999999999</v>
+        <v>11.407</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.985</v>
+        <v>14.862</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>11.725</v>
+        <v>14.897</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>12.828</v>
+        <v>16.281</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>17.573</v>
+        <v>24.463</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>23.649</v>
+        <v>31.922</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>22.172</v>
+        <v>29.065</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>23.417</v>
+        <v>29.381</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>24.774</v>
+        <v>31.513</v>
       </c>
     </row>
     <row r="42">
@@ -2792,37 +2792,37 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.869</v>
+        <v>1.097</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.858</v>
+        <v>1.69</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.363</v>
+        <v>12.832</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14.955</v>
+        <v>12.078</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.304</v>
+        <v>0.132</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>21.421</v>
+        <v>17.968</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.146000000000001</v>
+        <v>1.256</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.866</v>
+        <v>3.593</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.969</v>
+        <v>5.076</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>12.36</v>
+        <v>6.396</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.786</v>
+        <v>6.047</v>
       </c>
     </row>
     <row r="49">
@@ -19264,7 +19264,11 @@
           <t>Deferred income tax expense 11</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -21690,7 +21694,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -24371,7 +24379,11 @@
           <t>Deferred income tax expense 12</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -25704,7 +25716,11 @@
           <t>Deferred income tax expense 14</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27217,7 +27233,11 @@
           <t>Deferred income tax expense (recovery) 12</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -28981,7 +29001,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -30182,7 +30206,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -31989,7 +32017,11 @@
           <t>Deferred income tax expense 17</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -33490,7 +33522,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -34687,7 +34723,11 @@
           <t>Deferred income tax expense 15</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" s="5" t="n">
         <v>6.142</v>
       </c>
@@ -39629,7 +39669,11 @@
           <t>Deferred income tax recovery (expense) 12</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -45121,7 +45165,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -46908,7 +46956,11 @@
           <t>Deferred income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
